--- a/Capstone/Forces and Safety Factors.xlsx
+++ b/Capstone/Forces and Safety Factors.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\School\Capstone\Capstone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAF3C21E-D6D6-4A6E-AC06-6AB08CB56480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABDE8722-CB75-4DAC-AA20-E7F43011481B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BDD5A3D1-9FC0-4A6F-B548-E58B049B64D9}"/>
   </bookViews>
@@ -96,15 +96,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -112,20 +118,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -134,7 +156,25 @@
   </cellStyles>
   <dxfs count="12">
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -183,13 +223,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B996EC48-B5B6-4003-9C6F-EEEB423329C6}" name="Table1" displayName="Table1" ref="C3:L10" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B996EC48-B5B6-4003-9C6F-EEEB423329C6}" name="Table1" displayName="Table1" ref="C3:L10" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
   <autoFilter ref="C3:L10" xr:uid="{B996EC48-B5B6-4003-9C6F-EEEB423329C6}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{91990692-5AA5-4310-9746-7666675FCFA4}" name="Iteration" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{732697A9-85F6-4065-BF18-8CFA2CC4E753}" name="L" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{66C70103-59F6-4AE4-8D74-D9892C6854BC}" name="w" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{D810107A-D010-4F23-82E4-7D662AD43AA9}" name="h" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{91990692-5AA5-4310-9746-7666675FCFA4}" name="Iteration" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{732697A9-85F6-4065-BF18-8CFA2CC4E753}" name="L" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{66C70103-59F6-4AE4-8D74-D9892C6854BC}" name="w" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{D810107A-D010-4F23-82E4-7D662AD43AA9}" name="h" dataDxfId="0"/>
     <tableColumn id="5" xr3:uid="{51B6EB76-3294-47A6-A78A-C3CB9903BA34}" name="n_nylon" dataDxfId="7"/>
     <tableColumn id="6" xr3:uid="{A3F6C762-C30C-4008-B9B8-C4D378A638CD}" name="F_nylon" dataDxfId="6"/>
     <tableColumn id="7" xr3:uid="{35EF7D11-5375-45FC-B9BB-0A769E005834}" name="n_delrin" dataDxfId="5"/>
@@ -518,7 +558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9E32BC8-EEF2-40DE-9498-D3AB0501051A}">
-  <dimension ref="C1:M43"/>
+  <dimension ref="C1:L43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10" customWidth="1"/>
@@ -530,659 +570,659 @@
     <col min="12" max="12" width="14.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="G1" s="1" t="s">
+    <row r="1" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="G1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-    </row>
-    <row r="2" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="G2" s="1" t="s">
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="G2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1" t="s">
+      <c r="H2" s="3"/>
+      <c r="I2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1" t="s">
+      <c r="J2" s="3"/>
+      <c r="K2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="1"/>
-    </row>
-    <row r="3" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C3" s="3" t="s">
+      <c r="L2" s="3"/>
+    </row>
+    <row r="3" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C4" s="3">
+    <row r="4" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C4" s="1">
         <v>1</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="1">
         <v>19.2</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="1">
+        <v>2.9</v>
+      </c>
+      <c r="F4" s="4">
         <v>2</v>
       </c>
-      <c r="F4" s="3">
+      <c r="G4" s="1">
+        <v>0.41</v>
+      </c>
+      <c r="H4" s="1">
+        <v>6.22</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.49</v>
+      </c>
+      <c r="J4" s="1">
+        <v>7.78</v>
+      </c>
+      <c r="K4" s="1">
+        <v>0.89</v>
+      </c>
+      <c r="L4" s="1">
+        <v>5.05</v>
+      </c>
+    </row>
+    <row r="5" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C5" s="1">
+        <v>2</v>
+      </c>
+      <c r="D5" s="1">
+        <v>19.2</v>
+      </c>
+      <c r="E5" s="1">
         <v>2.9</v>
       </c>
-      <c r="G4" s="3">
-        <v>0.41</v>
-      </c>
-      <c r="H4" s="3">
-        <v>6.22</v>
-      </c>
-      <c r="I4" s="3">
-        <v>0.49</v>
-      </c>
-      <c r="J4" s="3">
-        <v>7.78</v>
-      </c>
-      <c r="K4" s="3">
-        <v>0.89</v>
-      </c>
-      <c r="L4" s="3">
-        <v>5.05</v>
-      </c>
-      <c r="M4" s="2"/>
-    </row>
-    <row r="5" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C5" s="3">
+      <c r="F5" s="5">
+        <v>1.8</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.51</v>
+      </c>
+      <c r="H5" s="1">
+        <v>4.54</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.61</v>
+      </c>
+      <c r="J5" s="1">
+        <v>5.67</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L5" s="1">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="6" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C6" s="1">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1">
+        <v>19.2</v>
+      </c>
+      <c r="E6" s="1">
+        <v>2.9</v>
+      </c>
+      <c r="F6" s="4">
+        <v>1.6</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="H6" s="1">
+        <v>3.19</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0.77</v>
+      </c>
+      <c r="J6" s="1">
+        <v>3.98</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1.39</v>
+      </c>
+      <c r="L6" s="1">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="7" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C7" s="1">
+        <v>4</v>
+      </c>
+      <c r="D7" s="1">
+        <v>19.2</v>
+      </c>
+      <c r="E7" s="1">
+        <v>2.9</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1.4</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.84</v>
+      </c>
+      <c r="H7" s="1">
+        <v>2.13</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1.01</v>
+      </c>
+      <c r="J7" s="1">
+        <v>2.67</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1.81</v>
+      </c>
+      <c r="L7" s="1">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="8" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C8" s="1">
+        <v>5</v>
+      </c>
+      <c r="D8" s="1">
+        <v>19.2</v>
+      </c>
+      <c r="E8" s="1">
+        <v>2.9</v>
+      </c>
+      <c r="F8" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1.34</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1.37</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1.68</v>
+      </c>
+      <c r="K8" s="1">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="L8" s="1">
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C9" s="1">
+        <v>6</v>
+      </c>
+      <c r="D9" s="1">
+        <v>19.2</v>
+      </c>
+      <c r="E9" s="1">
+        <v>2.9</v>
+      </c>
+      <c r="F9" s="5">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1.64</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0.78</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1.97</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="K9" s="1">
+        <v>3.55</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="10" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C10" s="1">
+        <v>7</v>
+      </c>
+      <c r="D10" s="1">
+        <v>19.2</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2.9</v>
+      </c>
+      <c r="F10" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="G10" s="1">
+        <v>2.57</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="I10" s="1">
+        <v>3.08</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="K10" s="1">
+        <v>5.55</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="11" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+    </row>
+    <row r="12" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+    </row>
+    <row r="13" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="3">
-        <v>19.2</v>
-      </c>
-      <c r="E5" s="3">
-        <v>1.8</v>
-      </c>
-      <c r="F5" s="3">
-        <v>2.9</v>
-      </c>
-      <c r="G5" s="3">
-        <v>0.51</v>
-      </c>
-      <c r="H5" s="3">
-        <v>4.54</v>
-      </c>
-      <c r="I5" s="3">
-        <v>0.61</v>
-      </c>
-      <c r="J5" s="3">
-        <v>5.67</v>
-      </c>
-      <c r="K5" s="3">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="L5" s="3">
-        <v>3.68</v>
-      </c>
-    </row>
-    <row r="6" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C6" s="3">
-        <v>3</v>
-      </c>
-      <c r="D6" s="3">
-        <v>19.2</v>
-      </c>
-      <c r="E6" s="3">
-        <v>1.6</v>
-      </c>
-      <c r="F6" s="3">
-        <v>2.9</v>
-      </c>
-      <c r="G6" s="3">
-        <v>0.64</v>
-      </c>
-      <c r="H6" s="3">
-        <v>3.19</v>
-      </c>
-      <c r="I6" s="3">
-        <v>0.77</v>
-      </c>
-      <c r="J6" s="3">
-        <v>3.98</v>
-      </c>
-      <c r="K6" s="3">
-        <v>1.39</v>
-      </c>
-      <c r="L6" s="3">
-        <v>2.59</v>
-      </c>
-    </row>
-    <row r="7" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C7" s="3">
-        <v>4</v>
-      </c>
-      <c r="D7" s="3">
-        <v>19.2</v>
-      </c>
-      <c r="E7" s="3">
-        <v>1.4</v>
-      </c>
-      <c r="F7" s="3">
-        <v>2.9</v>
-      </c>
-      <c r="G7" s="3">
-        <v>0.84</v>
-      </c>
-      <c r="H7" s="3">
-        <v>2.13</v>
-      </c>
-      <c r="I7" s="3">
-        <v>1.01</v>
-      </c>
-      <c r="J7" s="3">
-        <v>2.67</v>
-      </c>
-      <c r="K7" s="3">
-        <v>1.81</v>
-      </c>
-      <c r="L7" s="3">
-        <v>1.73</v>
-      </c>
-    </row>
-    <row r="8" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C8" s="3">
-        <v>5</v>
-      </c>
-      <c r="D8" s="3">
-        <v>19.2</v>
-      </c>
-      <c r="E8" s="3">
-        <v>1.2</v>
-      </c>
-      <c r="F8" s="3">
-        <v>2.9</v>
-      </c>
-      <c r="G8" s="3">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="H8" s="3">
-        <v>1.34</v>
-      </c>
-      <c r="I8" s="3">
-        <v>1.37</v>
-      </c>
-      <c r="J8" s="3">
-        <v>1.68</v>
-      </c>
-      <c r="K8" s="3">
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="L8" s="3">
-        <v>1.0900000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C9" s="3">
-        <v>6</v>
-      </c>
-      <c r="D9" s="3">
-        <v>19.2</v>
-      </c>
-      <c r="E9" s="3">
+      <c r="F15" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F9" s="3">
-        <v>2.9</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1.64</v>
-      </c>
-      <c r="H9" s="3">
-        <v>0.78</v>
-      </c>
-      <c r="I9" s="3">
-        <v>1.97</v>
-      </c>
-      <c r="J9" s="3">
-        <v>0.97</v>
-      </c>
-      <c r="K9" s="3">
-        <v>3.55</v>
-      </c>
-      <c r="L9" s="3">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="10" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C10" s="3">
-        <v>7</v>
-      </c>
-      <c r="D10" s="3">
-        <v>19.2</v>
-      </c>
-      <c r="E10" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="F10" s="3">
-        <v>2.9</v>
-      </c>
-      <c r="G10" s="3">
-        <v>2.57</v>
-      </c>
-      <c r="H10" s="3">
-        <v>0.4</v>
-      </c>
-      <c r="I10" s="3">
-        <v>3.08</v>
-      </c>
-      <c r="J10" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="K10" s="3">
-        <v>5.55</v>
-      </c>
-      <c r="L10" s="3">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="11" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-    </row>
-    <row r="14" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="H14" s="4"/>
-      <c r="I14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L14" s="1"/>
-    </row>
-    <row r="15" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C15" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="H15" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="I15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="J15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K15" s="3" t="s">
+      <c r="K15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L15" s="3" t="s">
+      <c r="L15" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C16" s="3"/>
+    <row r="16" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C16" s="1"/>
     </row>
     <row r="17" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C17" s="3"/>
+      <c r="C17" s="1"/>
     </row>
     <row r="18" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C18" s="3"/>
+      <c r="C18" s="1"/>
     </row>
     <row r="19" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C19" s="3"/>
+      <c r="C19" s="1"/>
     </row>
     <row r="20" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C20" s="3"/>
+      <c r="C20" s="1"/>
     </row>
     <row r="21" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
     </row>
     <row r="22" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C22" s="3"/>
+      <c r="C22" s="1"/>
     </row>
     <row r="23" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
     </row>
     <row r="24" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
     </row>
     <row r="25" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
     </row>
     <row r="26" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
     </row>
     <row r="27" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
     </row>
     <row r="28" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
     </row>
     <row r="29" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
     </row>
     <row r="30" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
     </row>
     <row r="31" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
     </row>
     <row r="32" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
     </row>
     <row r="33" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
     </row>
     <row r="34" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
     </row>
     <row r="35" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
     </row>
     <row r="36" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
     </row>
     <row r="37" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
-      <c r="J37" s="3"/>
-      <c r="K37" s="3"/>
-      <c r="L37" s="3"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
     </row>
     <row r="38" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
-      <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
     </row>
     <row r="39" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
     </row>
     <row r="40" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
-      <c r="L40" s="3"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
     </row>
     <row r="41" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
     </row>
     <row r="42" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
     </row>
     <row r="43" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
-      <c r="J43" s="3"/>
-      <c r="K43" s="3"/>
-      <c r="L43" s="3"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="G1:L1"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="I14:J14"/>
     <mergeCell ref="K14:L14"/>
@@ -1190,7 +1230,6 @@
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
